--- a/КАТАЛОГ.xlsx
+++ b/КАТАЛОГ.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Як оновлювати" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Каталог'!$A$1:$I$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Каталог'!$A$1:$I$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -523,7 +523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -587,7 +587,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Вітамін D3</t>
+          <t>Вітамін A</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -602,11 +602,11 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>120 капсул · 2000 МО</t>
+          <t>100 капсул · 3000 мкг (10 000 МО)</t>
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="F2" s="3" t="n"/>
       <c r="G2" s="2" t="inlineStr">
@@ -614,11 +614,7 @@
           <t>так</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>products/d3.jpg</t>
-        </is>
-      </c>
+      <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr">
         <is>
           <t>https://www.kidstaff.com.ua/tema-30954663.html</t>
@@ -628,26 +624,26 @@
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Таурат магнію+</t>
+          <t>Вітамін D3</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>KAL</t>
+          <t>NOW Foods</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Мінерали</t>
+          <t>Вітаміни</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>180 таблеток</t>
+          <t>120 капсул · 2000 МО</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>1160</v>
+        <v>215</v>
       </c>
       <c r="F3" s="3" t="n"/>
       <c r="G3" s="2" t="inlineStr">
@@ -657,38 +653,38 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>products/magnesium.jpg</t>
+          <t>products/d3.jpg</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>https://www.kidstaff.com.ua/tema-32556516.html</t>
+          <t>https://www.kidstaff.com.ua/tema-30954663.html</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Омега-3</t>
+          <t>Вітамін D3 5000</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>NOW Foods</t>
+          <t>California Gold Nutrition</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Омега</t>
+          <t>Вітаміни</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>100 капсул · риб’ячий жир 1000 мг</t>
+          <t>90 капсул · 125 мкг (5000 МО)</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>335</v>
+        <v>195</v>
       </c>
       <c r="F4" s="3" t="n"/>
       <c r="G4" s="2" t="inlineStr">
@@ -696,40 +692,36 @@
           <t>так</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>products/omega-now.jpg</t>
-        </is>
-      </c>
+      <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>https://www.kidstaff.com.ua/tema-32628562.html</t>
+          <t>https://www.kidstaff.com.ua/tema-30954663.html</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Омега-800</t>
+          <t>Вітамін С, аскорбат натрію</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>California Gold Nutrition</t>
+          <t>NutriBiotic</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Омега</t>
+          <t>Вітаміни</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30 капсул · омега-3 800 мг</t>
+          <t>227 г · кристалічний порошок</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>345</v>
+        <v>460</v>
       </c>
       <c r="F5" s="3" t="n"/>
       <c r="G5" s="2" t="inlineStr">
@@ -737,40 +729,32 @@
           <t>так</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>products/omega-cgn.jpg</t>
-        </is>
-      </c>
+      <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>https://www.kidstaff.com.ua/tema-32628562.html</t>
+          <t>https://www.kidstaff.com.ua/tema-31033109.html</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Цитрат цинку</t>
+          <t>Вітамін С, желейки апельсин</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>21st Century</t>
+          <t>California Gold Nutrition</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Мінерали</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>60 таблеток · 50 мг</t>
-        </is>
-      </c>
+          <t>Вітаміни</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
       <c r="E6" s="3" t="n">
-        <v>110</v>
+        <v>300</v>
       </c>
       <c r="F6" s="3" t="n"/>
       <c r="G6" s="2" t="inlineStr">
@@ -778,40 +762,34 @@
           <t>так</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>products/zinc.jpg</t>
-        </is>
-      </c>
+      <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>https://www.kidstaff.com.ua/tema-32355256.html</t>
+          <t>https://www.kidstaff.com.ua/tema-31033212.html</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Комплекс вітамінів B</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Life Extension</t>
-        </is>
-      </c>
+          <t>Вітаміни C, D3, K2, B, A та комплекси для імунітету</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Комплекси</t>
+          <t>Вітаміни</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>60 вегетаріанських капсул</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>405</v>
+          <t>кілька позицій в оголошенні</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>від 135</t>
+        </is>
       </c>
       <c r="F7" s="3" t="n"/>
       <c r="G7" s="2" t="inlineStr">
@@ -819,11 +797,7 @@
           <t>так</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>products/b-complex.jpg</t>
-        </is>
-      </c>
+      <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="inlineStr">
         <is>
           <t>https://www.kidstaff.com.ua/tema-30954663.html</t>
@@ -833,26 +807,28 @@
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Hema-Plex</t>
+          <t>Вітаміни D3 і K2</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>NaturesPlus</t>
+          <t>Futurebiotics</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Комплекси</t>
+          <t>Вітаміни</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>30 таблеток · тривале вивільнення</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>425</v>
+          <t>60 капсул</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>від 285</t>
+        </is>
       </c>
       <c r="F8" s="3" t="n"/>
       <c r="G8" s="2" t="inlineStr">
@@ -860,14 +836,10 @@
           <t>так</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>products/hema-plex.jpg</t>
-        </is>
-      </c>
+      <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>https://www.kidstaff.com.ua/tema-30756832.html</t>
+          <t>https://www.kidstaff.com.ua/tema-30757138.html</t>
         </is>
       </c>
     </row>
@@ -912,225 +884,765 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="n"/>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="4" t="n"/>
-      <c r="H10" s="4" t="n"/>
-      <c r="I10" s="4" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="n"/>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="4" t="n"/>
-      <c r="H11" s="4" t="n"/>
-      <c r="I11" s="4" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="n"/>
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="4" t="n"/>
-      <c r="H12" s="4" t="n"/>
-      <c r="I12" s="4" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="n"/>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="4" t="n"/>
-      <c r="H13" s="4" t="n"/>
-      <c r="I13" s="4" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="n"/>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="4" t="n"/>
-      <c r="H14" s="4" t="n"/>
-      <c r="I14" s="4" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="n"/>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="4" t="n"/>
-      <c r="D15" s="4" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="4" t="n"/>
-      <c r="H15" s="4" t="n"/>
-      <c r="I15" s="4" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="n"/>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="4" t="n"/>
-      <c r="H16" s="4" t="n"/>
-      <c r="I16" s="4" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="n"/>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="4" t="n"/>
-      <c r="D17" s="4" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="4" t="n"/>
-      <c r="H17" s="4" t="n"/>
-      <c r="I17" s="4" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="n"/>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="4" t="n"/>
-      <c r="D18" s="4" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="4" t="n"/>
-      <c r="H18" s="4" t="n"/>
-      <c r="I18" s="4" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="n"/>
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="4" t="n"/>
-      <c r="D19" s="4" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="4" t="n"/>
-      <c r="H19" s="4" t="n"/>
-      <c r="I19" s="4" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="n"/>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="4" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="4" t="n"/>
-      <c r="H20" s="4" t="n"/>
-      <c r="I20" s="4" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="n"/>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="4" t="n"/>
-      <c r="H21" s="4" t="n"/>
-      <c r="I21" s="4" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="n"/>
-      <c r="B22" s="4" t="n"/>
-      <c r="C22" s="4" t="n"/>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="4" t="n"/>
-      <c r="H22" s="4" t="n"/>
-      <c r="I22" s="4" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="n"/>
-      <c r="B23" s="4" t="n"/>
-      <c r="C23" s="4" t="n"/>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="4" t="n"/>
-      <c r="H23" s="4" t="n"/>
-      <c r="I23" s="4" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="n"/>
-      <c r="B24" s="4" t="n"/>
-      <c r="C24" s="4" t="n"/>
-      <c r="D24" s="4" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="4" t="n"/>
-      <c r="H24" s="4" t="n"/>
-      <c r="I24" s="4" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="n"/>
-      <c r="B25" s="4" t="n"/>
-      <c r="C25" s="4" t="n"/>
-      <c r="D25" s="4" t="n"/>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="n"/>
-      <c r="G25" s="4" t="n"/>
-      <c r="H25" s="4" t="n"/>
-      <c r="I25" s="4" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="n"/>
-      <c r="B26" s="4" t="n"/>
-      <c r="C26" s="4" t="n"/>
-      <c r="D26" s="4" t="n"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="n"/>
-      <c r="G26" s="4" t="n"/>
-      <c r="H26" s="4" t="n"/>
-      <c r="I26" s="4" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="n"/>
-      <c r="B27" s="4" t="n"/>
-      <c r="C27" s="4" t="n"/>
-      <c r="D27" s="4" t="n"/>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5" t="n"/>
-      <c r="G27" s="4" t="n"/>
-      <c r="H27" s="4" t="n"/>
-      <c r="I27" s="4" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="n"/>
-      <c r="B28" s="4" t="n"/>
-      <c r="C28" s="4" t="n"/>
-      <c r="D28" s="4" t="n"/>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5" t="n"/>
-      <c r="G28" s="4" t="n"/>
-      <c r="H28" s="4" t="n"/>
-      <c r="I28" s="4" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="n"/>
-      <c r="B29" s="4" t="n"/>
-      <c r="C29" s="4" t="n"/>
-      <c r="D29" s="4" t="n"/>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5" t="n"/>
-      <c r="G29" s="4" t="n"/>
-      <c r="H29" s="4" t="n"/>
-      <c r="I29" s="4" t="n"/>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Ultra-Mag, магній з вітамінами</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Source Naturals</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Мінерали</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>120 таблеток</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>від 330</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="n"/>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>так</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kidstaff.com.ua/tema-32294299.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Піколінат цинку</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Swanson</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Мінерали</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>60 капсул · 22 мг</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>145</v>
+      </c>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>так</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kidstaff.com.ua/tema-30954663.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Рідкий йод плюс</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Life-flo</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Мінерали</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>59 мл · 320 порцій</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>260</v>
+      </c>
+      <c r="F12" s="3" t="n"/>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>так</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kidstaff.com.ua/tema-30757022.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Таурат магнію+</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>KAL</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Мінерали</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>180 таблеток · 200 мг</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>1160</v>
+      </c>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>так</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>products/magnesium.jpg</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kidstaff.com.ua/tema-32556516.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Цитрат цинку</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>21st Century</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Мінерали</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>60 таблеток · 50 мг</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>110</v>
+      </c>
+      <c r="F14" s="3" t="n"/>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>так</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>products/zinc.jpg</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kidstaff.com.ua/tema-32355256.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Омега-3</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>NOW Foods</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Омега</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>100 капсул · риб’ячий жир 1000 мг</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>335</v>
+      </c>
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>так</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>products/omega-now.jpg</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kidstaff.com.ua/tema-32628562.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Омега-800</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>California Gold Nutrition</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Омега</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>30 капсул · омега-3 800 мг</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>345</v>
+      </c>
+      <c r="F16" s="3" t="n"/>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>так</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>products/omega-cgn.jpg</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kidstaff.com.ua/tema-32628562.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>CollagenUP, морський колаген з гіалуроновою кислотою</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>California Gold Nutrition</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Комплекси</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr"/>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>від 630</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="n"/>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>так</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kidstaff.com.ua/tema-30454798.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Hema-Plex</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>NaturesPlus</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Комплекси</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>30 таблеток · тривале вивільнення</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>425</v>
+      </c>
+      <c r="F18" s="3" t="n"/>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>так</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>products/hema-plex.jpg</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kidstaff.com.ua/tema-30756832.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Екстракт насіння грейпфрута GSE, рідкий концентрат</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>NutriBiotic</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Комплекси</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>118 мл</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>460</v>
+      </c>
+      <c r="F19" s="3" t="n"/>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>так</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kidstaff.com.ua/tema-31033166.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Здоров’я дихальних шляхів</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Natural Factors</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Комплекси</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>90 таблеток</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>390</v>
+      </c>
+      <c r="F20" s="3" t="n"/>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>так</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kidstaff.com.ua/tema-31034319.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Кверцетин і бромелаїн</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>NOW Foods</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Комплекси</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>від 525</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="n"/>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>так</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kidstaff.com.ua/tema-32853267.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Комплекс вітамінів B</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Life Extension</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Комплекси</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>60 вегетаріанських капсул</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>405</v>
+      </c>
+      <c r="F22" s="3" t="n"/>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>так</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>products/b-complex.jpg</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kidstaff.com.ua/tema-30954663.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Монолаурин Nature Life</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Nature’s Life</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Комплекси</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>60–90 шт · 500 мг</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>460</v>
+      </c>
+      <c r="F23" s="3" t="n"/>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>так</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kidstaff.com.ua/tema-30007984.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Alive! мультивітаміни для дітей</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Nature’s Way</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Для дітей</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr"/>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>від 400</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="n"/>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>так</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kidstaff.com.ua/tema-32317869.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Animal Parade Alive, дитячі мультивітаміни</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>NaturesPlus</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Для дітей</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr"/>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>від 400</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="n"/>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>так</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kidstaff.com.ua/tema-26908959.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Animal Parade, вітамін D3 для дітей</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>NaturesPlus</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Для дітей</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>смак черешні</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>від 195</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="n"/>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>так</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kidstaff.com.ua/tema-32556474.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Animal Parade, мультивітаміни для дітей</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>NaturesPlus</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Для дітей</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>90 / 180 шт</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>від 400</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="n"/>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>так</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kidstaff.com.ua/tema-26909058.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Колострум Colostrum Plus, жувальний</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Symbiotics</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Для дітей</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>черешня</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>910</v>
+      </c>
+      <c r="F28" s="3" t="n"/>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>так</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kidstaff.com.ua/tema-26949955.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Омега для дітей Kids Smart</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Carlson</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Для дітей</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr"/>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>від 300</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="n"/>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>так</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kidstaff.com.ua/tema-32344811.html</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n"/>
@@ -1253,8 +1765,228 @@
       <c r="H40" s="4" t="n"/>
       <c r="I40" s="4" t="n"/>
     </row>
+    <row r="41">
+      <c r="A41" s="4" t="n"/>
+      <c r="B41" s="4" t="n"/>
+      <c r="C41" s="4" t="n"/>
+      <c r="D41" s="4" t="n"/>
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="5" t="n"/>
+      <c r="G41" s="4" t="n"/>
+      <c r="H41" s="4" t="n"/>
+      <c r="I41" s="4" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n"/>
+      <c r="B42" s="4" t="n"/>
+      <c r="C42" s="4" t="n"/>
+      <c r="D42" s="4" t="n"/>
+      <c r="E42" s="5" t="n"/>
+      <c r="F42" s="5" t="n"/>
+      <c r="G42" s="4" t="n"/>
+      <c r="H42" s="4" t="n"/>
+      <c r="I42" s="4" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n"/>
+      <c r="B43" s="4" t="n"/>
+      <c r="C43" s="4" t="n"/>
+      <c r="D43" s="4" t="n"/>
+      <c r="E43" s="5" t="n"/>
+      <c r="F43" s="5" t="n"/>
+      <c r="G43" s="4" t="n"/>
+      <c r="H43" s="4" t="n"/>
+      <c r="I43" s="4" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n"/>
+      <c r="B44" s="4" t="n"/>
+      <c r="C44" s="4" t="n"/>
+      <c r="D44" s="4" t="n"/>
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="5" t="n"/>
+      <c r="G44" s="4" t="n"/>
+      <c r="H44" s="4" t="n"/>
+      <c r="I44" s="4" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="n"/>
+      <c r="B45" s="4" t="n"/>
+      <c r="C45" s="4" t="n"/>
+      <c r="D45" s="4" t="n"/>
+      <c r="E45" s="5" t="n"/>
+      <c r="F45" s="5" t="n"/>
+      <c r="G45" s="4" t="n"/>
+      <c r="H45" s="4" t="n"/>
+      <c r="I45" s="4" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="n"/>
+      <c r="B46" s="4" t="n"/>
+      <c r="C46" s="4" t="n"/>
+      <c r="D46" s="4" t="n"/>
+      <c r="E46" s="5" t="n"/>
+      <c r="F46" s="5" t="n"/>
+      <c r="G46" s="4" t="n"/>
+      <c r="H46" s="4" t="n"/>
+      <c r="I46" s="4" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="n"/>
+      <c r="B47" s="4" t="n"/>
+      <c r="C47" s="4" t="n"/>
+      <c r="D47" s="4" t="n"/>
+      <c r="E47" s="5" t="n"/>
+      <c r="F47" s="5" t="n"/>
+      <c r="G47" s="4" t="n"/>
+      <c r="H47" s="4" t="n"/>
+      <c r="I47" s="4" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="n"/>
+      <c r="B48" s="4" t="n"/>
+      <c r="C48" s="4" t="n"/>
+      <c r="D48" s="4" t="n"/>
+      <c r="E48" s="5" t="n"/>
+      <c r="F48" s="5" t="n"/>
+      <c r="G48" s="4" t="n"/>
+      <c r="H48" s="4" t="n"/>
+      <c r="I48" s="4" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="n"/>
+      <c r="B49" s="4" t="n"/>
+      <c r="C49" s="4" t="n"/>
+      <c r="D49" s="4" t="n"/>
+      <c r="E49" s="5" t="n"/>
+      <c r="F49" s="5" t="n"/>
+      <c r="G49" s="4" t="n"/>
+      <c r="H49" s="4" t="n"/>
+      <c r="I49" s="4" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="n"/>
+      <c r="B50" s="4" t="n"/>
+      <c r="C50" s="4" t="n"/>
+      <c r="D50" s="4" t="n"/>
+      <c r="E50" s="5" t="n"/>
+      <c r="F50" s="5" t="n"/>
+      <c r="G50" s="4" t="n"/>
+      <c r="H50" s="4" t="n"/>
+      <c r="I50" s="4" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="n"/>
+      <c r="B51" s="4" t="n"/>
+      <c r="C51" s="4" t="n"/>
+      <c r="D51" s="4" t="n"/>
+      <c r="E51" s="5" t="n"/>
+      <c r="F51" s="5" t="n"/>
+      <c r="G51" s="4" t="n"/>
+      <c r="H51" s="4" t="n"/>
+      <c r="I51" s="4" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="n"/>
+      <c r="B52" s="4" t="n"/>
+      <c r="C52" s="4" t="n"/>
+      <c r="D52" s="4" t="n"/>
+      <c r="E52" s="5" t="n"/>
+      <c r="F52" s="5" t="n"/>
+      <c r="G52" s="4" t="n"/>
+      <c r="H52" s="4" t="n"/>
+      <c r="I52" s="4" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="n"/>
+      <c r="B53" s="4" t="n"/>
+      <c r="C53" s="4" t="n"/>
+      <c r="D53" s="4" t="n"/>
+      <c r="E53" s="5" t="n"/>
+      <c r="F53" s="5" t="n"/>
+      <c r="G53" s="4" t="n"/>
+      <c r="H53" s="4" t="n"/>
+      <c r="I53" s="4" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="n"/>
+      <c r="B54" s="4" t="n"/>
+      <c r="C54" s="4" t="n"/>
+      <c r="D54" s="4" t="n"/>
+      <c r="E54" s="5" t="n"/>
+      <c r="F54" s="5" t="n"/>
+      <c r="G54" s="4" t="n"/>
+      <c r="H54" s="4" t="n"/>
+      <c r="I54" s="4" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="n"/>
+      <c r="B55" s="4" t="n"/>
+      <c r="C55" s="4" t="n"/>
+      <c r="D55" s="4" t="n"/>
+      <c r="E55" s="5" t="n"/>
+      <c r="F55" s="5" t="n"/>
+      <c r="G55" s="4" t="n"/>
+      <c r="H55" s="4" t="n"/>
+      <c r="I55" s="4" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="n"/>
+      <c r="B56" s="4" t="n"/>
+      <c r="C56" s="4" t="n"/>
+      <c r="D56" s="4" t="n"/>
+      <c r="E56" s="5" t="n"/>
+      <c r="F56" s="5" t="n"/>
+      <c r="G56" s="4" t="n"/>
+      <c r="H56" s="4" t="n"/>
+      <c r="I56" s="4" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="n"/>
+      <c r="B57" s="4" t="n"/>
+      <c r="C57" s="4" t="n"/>
+      <c r="D57" s="4" t="n"/>
+      <c r="E57" s="5" t="n"/>
+      <c r="F57" s="5" t="n"/>
+      <c r="G57" s="4" t="n"/>
+      <c r="H57" s="4" t="n"/>
+      <c r="I57" s="4" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="n"/>
+      <c r="B58" s="4" t="n"/>
+      <c r="C58" s="4" t="n"/>
+      <c r="D58" s="4" t="n"/>
+      <c r="E58" s="5" t="n"/>
+      <c r="F58" s="5" t="n"/>
+      <c r="G58" s="4" t="n"/>
+      <c r="H58" s="4" t="n"/>
+      <c r="I58" s="4" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="n"/>
+      <c r="B59" s="4" t="n"/>
+      <c r="C59" s="4" t="n"/>
+      <c r="D59" s="4" t="n"/>
+      <c r="E59" s="5" t="n"/>
+      <c r="F59" s="5" t="n"/>
+      <c r="G59" s="4" t="n"/>
+      <c r="H59" s="4" t="n"/>
+      <c r="I59" s="4" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="n"/>
+      <c r="B60" s="4" t="n"/>
+      <c r="C60" s="4" t="n"/>
+      <c r="D60" s="4" t="n"/>
+      <c r="E60" s="5" t="n"/>
+      <c r="F60" s="5" t="n"/>
+      <c r="G60" s="4" t="n"/>
+      <c r="H60" s="4" t="n"/>
+      <c r="I60" s="4" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I9"/>
+  <autoFilter ref="A1:I29"/>
   <dataValidations count="1">
     <dataValidation sqref="G2:G300" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Тільки так або ні" error="Введіть «так» або «ні» — або лишіть порожнім, це теж означає «є»." promptTitle="Наявність" prompt="так — товар є; ні — тимчасово немає. Порожньо = є." type="list">
       <formula1>"так,ні"</formula1>
